--- a/03_Outputs/Bioenergetica_Norte/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/03_Ordenamiento/ordenamiento.xlsx
@@ -16,6 +16,20 @@
     <sheet name="tti_edsup" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="internet_2025" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="uso_suelo_rural" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="_fig_01" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_fig_02" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="_fig_03" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_fig_04" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="_fig_05" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_06" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_07" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_08" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_09" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_10" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_11" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_fig_12" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_fig_13" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_fig_14" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
 </workbook>
 </file>
@@ -1435,6 +1449,2612 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.15097869566661</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.534574496012986</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.270116020859396</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.180285116103234</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.340186905218954</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.300109988211582</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.143171126425268</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.53383102720126</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.288747802724</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.258658277306015</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.253411364838396</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.295177446596649</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.255039730029715</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.687427922731711</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.687294638715807</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.6558639248779</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.673581311493321</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.362335636394915</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.574877401928597</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.742782358680706</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.729763708784726</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.519517214499171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.409691159428071</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.403845553884414</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.529703702674569</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.318238435143436</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.0400873284500982</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.0670298158898514</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.289606040359022</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.0405995375622717</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.212486288968215</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.0946641234143567</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.487476572417853</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.119733832902162</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.429444309699584</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.306258340884817</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.153254866182126</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>0.122566188369185</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0.242911837355881</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>0.0958192093473051</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0.517798013682005</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>0.012025770411889</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0.0657740356514282</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>0.291686833371828</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>0.327176295770876</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>0.27816414694807</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0.338268866671721</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>0.311779097203111</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>0.364249551472128</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>0.0961138784482969</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>0.0112761616798996</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>0.192872918896798</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>0.0544834167608284</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>0.0388717924309366</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>0.472611391127601</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1.13033338953416</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>1.89002465177849</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>8.16595642276528</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2.93945001282605</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>15.384234952799</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>4.20471329391572</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>21.6523340690118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>2.87469860984191</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>10.310560767788</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>10.9751732624012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>5.49209110450821</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>3.95311214225888</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>7.83460550194749</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>1.63537261436958</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>8.83740011129964</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1.19321819476477</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>6.52621606718858</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>7.94143813805682</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>8.9076708847906</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>9.06882618526614</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>11.0283858987244</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>8.02227595424822</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>9.37237436484369</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>3.73829145703461</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>0.438579522090407</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>7.5016761017826</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>0.880308359058089</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>0.628065672876939</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>7.63615395161522</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.0881274631548557</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0423594917702728</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0858936354210138</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.0615719764128022</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0195099935525467</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.0180677261457206</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.0264518518518519</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.108206574154355</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.0558075759213229</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.012653802213964</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.0942615384079453</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.05195709789952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.0177711189696238</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.254668212259529</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.455042253119616</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.550467610831063</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.482820531928899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.141378539395294</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.210959281450023</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.367578692678176</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.22507944018208</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.533425712769109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.272661529637665</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.343495011319353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.439073158053075</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.180016855526902</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.993049509714873</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Acueducto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.884982678254471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Alcantarillado</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.702731807269917</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Recolección de basuras</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.851174798025616</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.328072501657953</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gas natural</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.543381396070275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.992586544500931</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Acueducto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.93579635079431</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alcantarillado</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.866893560801633</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recolección de basuras</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.944698426552535</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.601239746666835</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gas natural</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.66955125810138</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adopción TIC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>8.92861182292848</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Capacidades</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>37.1623672684875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dinamismo de los negocios</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>55.5987827079859</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>49.4622045892582</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Innovación</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Instituciones</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>50.262103707152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mercado de bienes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>5.54533787649063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>40.4904757811993</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>44.4945373577139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sistema financiero</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>24.4968644671062</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tamaño del mercado</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>17.7393972949291</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Adopción TIC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>9.28015207353694</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Capacidades</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>41.9074122002197</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dinamismo de los negocios</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>58.4405416967164</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>50.6088657345118</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Innovación</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Instituciones</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>52.6170318351737</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mercado de bienes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>8.22485538099614</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>43.6804795248635</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>47.6738144536003</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sistema financiero</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>23.3042940081032</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tamaño del mercado</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Subregión Norte</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>21.5393670651105</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4.26941478587025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>5.91434732958735</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>6.18675588738366</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3.14838447914831</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>7.97953790090281</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>7.31763720020136</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4.60823533281327</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>4.16820068206878</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>6.14499246796124</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>8.73988866119368</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>3.8343531874922</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>8.66363689457211</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>18.7536726643183</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:P17"/>
@@ -2632,6 +5252,766 @@
       </c>
       <c r="P17" s="31">
         <v>0.66955125810138</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>53.85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>41.97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>52.36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>68.78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>64.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>89.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>64.84</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>63.34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>62.34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>72.44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>52.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gobernanza</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>60.3269740115704</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Innovación Pública Digital</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>16.0955247744372</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>29.6080399268607</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Seguridad y Privacidad</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>29.2146026797758</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Servicios Ciudadanos Digitales</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>18.0202043104223</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cultura y Apropiación</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>32.648709571056</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Servicios y Procesos Inteligentes</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>21.7696658973052</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Estado Abierto</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>78.4961326099338</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Decisiones basadas en datos</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>28.673581607266</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Proyectos de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ciudades y Territorios Inteligentes</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.138888888888889</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.203592814371257</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.384615384615385</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.153846153846154</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.473684210526316</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.544303797468354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.489795918367347</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.214611872146119</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.447761194029851</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.176470588235294</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.372093023255814</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.277777777777778</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.272357723577236</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>109.103988490129</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>464.939386736392</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>313.183360563026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>218.890554722639</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>564.94165398275</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>470.644943603586</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>204.023398487659</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>61.324750127054</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>213.455822750608</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>158.576051779935</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>121.268656716418</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>231.650459571067</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>432.145926845574</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.338461538461538</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.645705521472393</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0208667736757624</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.784931506849315</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.871576111360575</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.870544858664482</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.505594405594406</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.0812154696132597</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.836708860759494</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.601255886970173</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.172649572649573</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.205577918343876</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.872044198895028</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Bioenergetica_Norte/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/03_Ordenamiento/ordenamiento.xlsx
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E2" s="112">
-        <v>0.15097869566661</v>
+        <v>0.150978695666611</v>
       </c>
     </row>
     <row r="3">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="E3" s="112">
-        <v>0.534574496012986</v>
+        <v>0.534574496012987</v>
       </c>
     </row>
     <row r="4">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E7" s="112">
-        <v>0.300109988211582</v>
+        <v>0.300109988211583</v>
       </c>
     </row>
     <row r="8">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="E9" s="112">
-        <v>0.53383102720126</v>
+        <v>0.533831027201261</v>
       </c>
     </row>
     <row r="10">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="E12" s="112">
-        <v>0.253411364838396</v>
+        <v>0.253411364838397</v>
       </c>
     </row>
     <row r="13">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="E14" s="112">
-        <v>0.255039730029715</v>
+        <v>0.255039730029716</v>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.15097869566661</v>
+        <v>0.150978695666611</v>
       </c>
     </row>
     <row r="3">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.534574496012986</v>
+        <v>0.534574496012987</v>
       </c>
     </row>
     <row r="4">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.300109988211582</v>
+        <v>0.300109988211583</v>
       </c>
     </row>
     <row r="8">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.53383102720126</v>
+        <v>0.533831027201261</v>
       </c>
     </row>
     <row r="10">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.253411364838396</v>
+        <v>0.253411364838397</v>
       </c>
     </row>
     <row r="13">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.255039730029715</v>
+        <v>0.255039730029716</v>
       </c>
     </row>
   </sheetData>
